--- a/output/pdf_financials_xlsx/NEXX.xlsx
+++ b/output/pdf_financials_xlsx/NEXX.xlsx
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>5.290517</v>
       </c>
     </row>
     <row r="93">
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.129527</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>9.567043999999999</v>
+        <v>9.128425999999999</v>
       </c>
     </row>
     <row r="119">
@@ -2638,7 +2638,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -2912,7 +2916,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>-0.129527</v>
       </c>

--- a/output/pdf_financials_xlsx/NEXX.xlsx
+++ b/output/pdf_financials_xlsx/NEXX.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.312625</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.574371</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.312625</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.574371</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.332625</v>
+        <v>0.02</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.982967</v>
+        <v>0.408596</v>
       </c>
     </row>
     <row r="49">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/NEXX.xlsx
+++ b/output/pdf_financials_xlsx/NEXX.xlsx
@@ -517,7 +517,7 @@
         <v>0.044195</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.162607</v>
+        <v>0.176607</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         <v>0.067095</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.175528</v>
+        <v>0.189528</v>
       </c>
     </row>
     <row r="11">
@@ -569,7 +569,7 @@
         <v>-0.067095</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.175528</v>
+        <v>-0.189528</v>
       </c>
     </row>
     <row r="12">
@@ -2972,7 +2972,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.3925</v>
       </c>
@@ -3518,7 +3522,11 @@
           <t>Director fees 6</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
